--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9957,0.0001,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9692,0.0001,0.0006,0.0216</t>
-  </si>
-  <si>
-    <t>0.9650,0.0006,0.0035,0.0152</t>
-  </si>
-  <si>
-    <t>0.9750,0.0005,0.0016,0.0103</t>
-  </si>
-  <si>
-    <t>0.9409,0.0011,0.0008,0.0605</t>
-  </si>
-  <si>
-    <t>0.7959,0.0025,0.0009,0.2616</t>
-  </si>
-  <si>
-    <t>0.9456,0.0014,0.0021,0.0389</t>
-  </si>
-  <si>
-    <t>0.9674,0.0004,0.0002,0.0476</t>
-  </si>
-  <si>
-    <t>0.9386,0.0008,0.0002,0.0846</t>
-  </si>
-  <si>
-    <t>0.9304,0.0008,0.0002,0.0818</t>
-  </si>
-  <si>
-    <t>0.8824,0.0033,0.0026,0.1302</t>
-  </si>
-  <si>
-    <t>0.9547,0.0010,0.0005,0.0491</t>
-  </si>
-  <si>
-    <t>0.9382,0.0030,0.0938,0.0008</t>
-  </si>
-  <si>
-    <t>0.8829,0.0110,0.0770,0.0071</t>
-  </si>
-  <si>
-    <t>0.9726,0.0005,0.0263,0.0009</t>
-  </si>
-  <si>
-    <t>0.9100,0.0015,0.2046,0.0004</t>
-  </si>
-  <si>
-    <t>0.9796,0.0004,0.0031,0.0041</t>
-  </si>
-  <si>
-    <t>0.9697,0.0064,0.0093,0.0007</t>
-  </si>
-  <si>
-    <t>0.8526,0.0579,0.0396,0.0021</t>
-  </si>
-  <si>
-    <t>0.9774,0.0046,0.0021,0.0018</t>
-  </si>
-  <si>
-    <t>0.9586,0.0151,0.0095,0.0005</t>
-  </si>
-  <si>
-    <t>0.9065,0.0673,0.0113,0.0005</t>
-  </si>
-  <si>
-    <t>0.9607,0.0006,0.0411,0.0006</t>
-  </si>
-  <si>
-    <t>0.9858,0.0002,0.0027,0.0014</t>
-  </si>
-  <si>
-    <t>0.5707,0.0004,0.7072,0.0002</t>
-  </si>
-  <si>
-    <t>0.9578,0.0030,0.0306,0.0018</t>
-  </si>
-  <si>
-    <t>0.9323,0.0015,0.1101,0.0006</t>
-  </si>
-  <si>
-    <t>0.9405,0.0003,0.1598,0.0001</t>
-  </si>
-  <si>
-    <t>0.0458,0.0018,0.9730,0.0007</t>
-  </si>
-  <si>
-    <t>0.9884,0.0015,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.7956,0.0763,0.0973,0.0384</t>
-  </si>
-  <si>
-    <t>0.4366,0.0127,0.7106,0.0113</t>
-  </si>
-  <si>
-    <t>0.7641,0.0480,0.1782,0.0015</t>
-  </si>
-  <si>
-    <t>0.8830,0.0267,0.0225,0.0153</t>
-  </si>
-  <si>
-    <t>0.9811,0.0005,0.0029,0.0045</t>
-  </si>
-  <si>
-    <t>0.8259,0.0484,0.0278,0.0268</t>
-  </si>
-  <si>
-    <t>0.9702,0.0076,0.0068,0.0015</t>
-  </si>
-  <si>
-    <t>0.7145,0.0385,0.3394,0.0016</t>
-  </si>
-  <si>
-    <t>0.9742,0.0008,0.0189,0.0009</t>
-  </si>
-  <si>
-    <t>0.7109,0.0039,0.4595,0.0012</t>
-  </si>
-  <si>
-    <t>0.9020,0.0038,0.1008,0.0028</t>
-  </si>
-  <si>
-    <t>0.4588,0.0146,0.7800,0.0006</t>
-  </si>
-  <si>
-    <t>0.0731,0.9237,0.0336,0.0003</t>
-  </si>
-  <si>
-    <t>0.5251,0.0022,0.7247,0.0004</t>
-  </si>
-  <si>
-    <t>0.9650,0.0038,0.0053,0.0068</t>
-  </si>
-  <si>
-    <t>0.9778,0.0068,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.9705,0.0102,0.0022,0.0007</t>
-  </si>
-  <si>
-    <t>0.9913,0.0013,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.1960,0.0078,0.9312,0.0003</t>
-  </si>
-  <si>
-    <t>0.6636,0.0052,0.6144,0.0006</t>
-  </si>
-  <si>
-    <t>0.6702,0.0122,0.5281,0.0019</t>
-  </si>
-  <si>
-    <t>0.7302,0.0022,0.2523,0.0077</t>
-  </si>
-  <si>
-    <t>0.5991,0.0105,0.6376,0.0007</t>
-  </si>
-  <si>
-    <t>0.9311,0.0025,0.1331,0.0002</t>
-  </si>
-  <si>
-    <t>0.9789,0.0016,0.0014,0.0084</t>
-  </si>
-  <si>
-    <t>0.9663,0.0022,0.0005,0.0167</t>
-  </si>
-  <si>
-    <t>0.9556,0.0028,0.0030,0.0249</t>
-  </si>
-  <si>
-    <t>0.7467,0.0043,0.0785,0.0831</t>
-  </si>
-  <si>
-    <t>0.9469,0.0023,0.0016,0.0310</t>
-  </si>
-  <si>
-    <t>0.9630,0.0016,0.0014,0.0226</t>
-  </si>
-  <si>
-    <t>0.9454,0.0014,0.0016,0.0448</t>
-  </si>
-  <si>
-    <t>0.3013,0.0915,0.7467,0.0021</t>
-  </si>
-  <si>
-    <t>0.8943,0.0014,0.3016,0.0000</t>
-  </si>
-  <si>
-    <t>0.5424,0.0068,0.6733,0.0014</t>
-  </si>
-  <si>
-    <t>0.1932,0.5351,0.4299,0.0014</t>
-  </si>
-  <si>
-    <t>0.0532,0.0027,0.9834,0.0001</t>
-  </si>
-  <si>
-    <t>0.7350,0.1713,0.0655,0.0079</t>
-  </si>
-  <si>
-    <t>0.1327,0.9037,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.9651,0.0039,0.0091,0.0044</t>
-  </si>
-  <si>
-    <t>0.8898,0.0054,0.1235,0.0029</t>
-  </si>
-  <si>
-    <t>0.0352,0.0092,0.9684,0.0045</t>
-  </si>
-  <si>
-    <t>0.0046,0.6962,0.9848,0.0006</t>
-  </si>
-  <si>
-    <t>0.9088,0.0062,0.1045,0.0005</t>
-  </si>
-  <si>
-    <t>0.2609,0.6387,0.1664,0.0022</t>
-  </si>
-  <si>
-    <t>0.2996,0.4404,0.2644,0.0014</t>
-  </si>
-  <si>
-    <t>0.8648,0.0001,0.0010,0.1807</t>
-  </si>
-  <si>
-    <t>0.9296,0.0004,0.0006,0.1039</t>
-  </si>
-  <si>
-    <t>0.8192,0.0002,0.0006,0.3608</t>
-  </si>
-  <si>
-    <t>0.5295,0.0005,0.0008,0.7607</t>
-  </si>
-  <si>
-    <t>0.8682,0.0001,0.0007,0.1907</t>
-  </si>
-  <si>
-    <t>0.9778,0.0003,0.0011,0.0101</t>
-  </si>
-  <si>
-    <t>0.1231,0.1240,0.8792,0.0002</t>
-  </si>
-  <si>
-    <t>0.1372,0.0183,0.9627,0.0001</t>
-  </si>
-  <si>
-    <t>0.6964,0.0195,0.4237,0.0004</t>
-  </si>
-  <si>
-    <t>0.3155,0.0048,0.8647,0.0001</t>
-  </si>
-  <si>
-    <t>0.8064,0.0256,0.2111,0.0006</t>
-  </si>
-  <si>
-    <t>0.8589,0.0077,0.2474,0.0006</t>
-  </si>
-  <si>
-    <t>0.9649,0.0005,0.0008,0.0305</t>
-  </si>
-  <si>
-    <t>0.9747,0.0008,0.0005,0.0147</t>
-  </si>
-  <si>
-    <t>0.9604,0.0019,0.0008,0.0269</t>
-  </si>
-  <si>
-    <t>0.9006,0.0073,0.0052,0.0502</t>
-  </si>
-  <si>
-    <t>0.8919,0.0032,0.0024,0.0984</t>
-  </si>
-  <si>
-    <t>0.8970,0.0008,0.0006,0.1426</t>
-  </si>
-  <si>
-    <t>0.9445,0.0002,0.0002,0.1102</t>
-  </si>
-  <si>
-    <t>0.9234,0.0072,0.0004,0.0181</t>
-  </si>
-  <si>
-    <t>0.9880,0.0001,0.0000,0.0174</t>
-  </si>
-  <si>
-    <t>0.9015,0.0005,0.0005,0.1656</t>
-  </si>
-  <si>
-    <t>0.7905,0.0007,0.0002,0.3565</t>
-  </si>
-  <si>
-    <t>0.8710,0.0011,0.0006,0.2017</t>
-  </si>
-  <si>
-    <t>0.9439,0.0024,0.0006,0.0346</t>
-  </si>
-  <si>
-    <t>0.9318,0.0038,0.0012,0.0384</t>
-  </si>
-  <si>
-    <t>0.9650,0.0017,0.0006,0.0253</t>
-  </si>
-  <si>
-    <t>0.9056,0.0007,0.0004,0.1468</t>
-  </si>
-  <si>
-    <t>0.0778,0.0130,0.9729,0.0010</t>
-  </si>
-  <si>
-    <t>0.4464,0.0175,0.7408,0.0014</t>
-  </si>
-  <si>
-    <t>0.9504,0.0019,0.0326,0.0020</t>
-  </si>
-  <si>
-    <t>0.9582,0.0005,0.0386,0.0012</t>
-  </si>
-  <si>
-    <t>0.5843,0.3335,0.0273,0.0043</t>
-  </si>
-  <si>
-    <t>0.9496,0.0122,0.0045,0.0030</t>
-  </si>
-  <si>
-    <t>0.9777,0.0074,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.5069,0.2814,0.0488,0.0232</t>
-  </si>
-  <si>
-    <t>0.9502,0.0143,0.0080,0.0028</t>
-  </si>
-  <si>
-    <t>0.5289,0.2738,0.1372,0.0218</t>
-  </si>
-  <si>
-    <t>0.9780,0.0024,0.0027,0.0050</t>
-  </si>
-  <si>
-    <t>0.9627,0.0008,0.0156,0.0028</t>
-  </si>
-  <si>
-    <t>0.8995,0.0053,0.1507,0.0022</t>
-  </si>
-  <si>
-    <t>0.9791,0.0010,0.0061,0.0014</t>
-  </si>
-  <si>
-    <t>0.9768,0.0012,0.0074,0.0021</t>
-  </si>
-  <si>
-    <t>0.9706,0.0003,0.0019,0.0122</t>
-  </si>
-  <si>
-    <t>0.9972,0.0006,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9809,0.0059,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9127,0.0139,0.0610,0.0048</t>
-  </si>
-  <si>
-    <t>0.7460,0.1505,0.0317,0.0005</t>
-  </si>
-  <si>
-    <t>0.9757,0.0039,0.0036,0.0012</t>
-  </si>
-  <si>
-    <t>0.8837,0.0687,0.0159,0.0052</t>
-  </si>
-  <si>
-    <t>0.8578,0.0282,0.0260,0.0281</t>
-  </si>
-  <si>
-    <t>0.9789,0.0011,0.0018,0.0070</t>
-  </si>
-  <si>
-    <t>0.9387,0.0077,0.0043,0.0289</t>
-  </si>
-  <si>
-    <t>0.9685,0.0006,0.0004,0.0326</t>
-  </si>
-  <si>
-    <t>0.9436,0.0052,0.0059,0.0187</t>
-  </si>
-  <si>
-    <t>0.8920,0.0002,0.0005,0.1895</t>
-  </si>
-  <si>
-    <t>0.9891,0.0010,0.0006,0.0020</t>
-  </si>
-  <si>
-    <t>0.9445,0.0054,0.0021,0.0193</t>
-  </si>
-  <si>
-    <t>0.9196,0.0007,0.0012,0.0928</t>
-  </si>
-  <si>
-    <t>0.7150,0.0195,0.4698,0.0008</t>
-  </si>
-  <si>
-    <t>0.2430,0.0475,0.8587,0.0003</t>
-  </si>
-  <si>
-    <t>0.1193,0.0043,0.9588,0.0003</t>
-  </si>
-  <si>
-    <t>0.8101,0.0043,0.3382,0.0003</t>
-  </si>
-  <si>
-    <t>0.9935,0.0002,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9842,0.0007,0.0061,0.0008</t>
-  </si>
-  <si>
-    <t>0.9272,0.0006,0.0597,0.0027</t>
-  </si>
-  <si>
-    <t>0.9507,0.0022,0.0119,0.0057</t>
-  </si>
-  <si>
-    <t>0.9720,0.0001,0.0004,0.0251</t>
-  </si>
-  <si>
-    <t>0.5442,0.0004,0.0015,0.6819</t>
-  </si>
-  <si>
-    <t>0.9334,0.0002,0.0005,0.1114</t>
-  </si>
-  <si>
-    <t>0.9305,0.0004,0.0094,0.0299</t>
-  </si>
-  <si>
-    <t>0.1798,0.8034,0.0205,0.0003</t>
-  </si>
-  <si>
-    <t>0.9508,0.0004,0.0005,0.0703</t>
-  </si>
-  <si>
-    <t>0.9065,0.0049,0.0009,0.0300</t>
-  </si>
-  <si>
-    <t>0.9639,0.0009,0.0021,0.0188</t>
-  </si>
-  <si>
-    <t>0.9453,0.0024,0.0040,0.0248</t>
-  </si>
-  <si>
-    <t>0.9757,0.0022,0.0032,0.0073</t>
-  </si>
-  <si>
-    <t>0.9498,0.0007,0.0003,0.0505</t>
-  </si>
-  <si>
-    <t>0.8905,0.0006,0.0003,0.1591</t>
-  </si>
-  <si>
-    <t>0.1626,0.1588,0.8040,0.0659</t>
-  </si>
-  <si>
-    <t>0.9050,0.0003,0.0005,0.1151</t>
-  </si>
-  <si>
-    <t>0.8851,0.0008,0.0004,0.1413</t>
-  </si>
-  <si>
-    <t>0.9482,0.0112,0.0080,0.0048</t>
-  </si>
-  <si>
-    <t>0.9743,0.0021,0.0070,0.0036</t>
-  </si>
-  <si>
-    <t>0.9556,0.0053,0.0092,0.0056</t>
-  </si>
-  <si>
-    <t>0.9729,0.0023,0.0094,0.0022</t>
-  </si>
-  <si>
-    <t>0.9798,0.0013,0.0053,0.0017</t>
-  </si>
-  <si>
-    <t>0.9940,0.0002,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9069,0.0019,0.0017,0.1139</t>
-  </si>
-  <si>
-    <t>0.9436,0.0005,0.0003,0.0768</t>
-  </si>
-  <si>
-    <t>0.9161,0.0030,0.0012,0.0693</t>
-  </si>
-  <si>
-    <t>0.9246,0.0018,0.0011,0.0819</t>
-  </si>
-  <si>
-    <t>0.9845,0.0008,0.0003,0.0081</t>
-  </si>
-  <si>
-    <t>0.8683,0.0006,0.0014,0.1868</t>
-  </si>
-  <si>
-    <t>0.9888,0.0002,0.0001,0.0079</t>
-  </si>
-  <si>
-    <t>0.9553,0.0054,0.0043,0.0122</t>
-  </si>
-  <si>
-    <t>0.9565,0.0052,0.0019,0.0101</t>
-  </si>
-  <si>
-    <t>0.9531,0.0042,0.0099,0.0092</t>
-  </si>
-  <si>
-    <t>0.9790,0.0026,0.0027,0.0027</t>
-  </si>
-  <si>
-    <t>0.9372,0.0121,0.0021,0.0074</t>
-  </si>
-  <si>
-    <t>0.9632,0.0016,0.0009,0.0253</t>
-  </si>
-  <si>
-    <t>0.9428,0.0083,0.0115,0.0139</t>
-  </si>
-  <si>
-    <t>0.9525,0.0046,0.0030,0.0140</t>
-  </si>
-  <si>
-    <t>0.9366,0.0070,0.0044,0.0190</t>
-  </si>
-  <si>
-    <t>0.0362,0.0906,0.9702,0.0022</t>
-  </si>
-  <si>
-    <t>0.9301,0.0032,0.0008,0.0334</t>
-  </si>
-  <si>
-    <t>0.9671,0.0008,0.0586,0.0002</t>
-  </si>
-  <si>
-    <t>0.8947,0.0010,0.2124,0.0003</t>
-  </si>
-  <si>
-    <t>0.7687,0.0149,0.2475,0.0147</t>
-  </si>
-  <si>
-    <t>0.1568,0.1136,0.8980,0.0039</t>
-  </si>
-  <si>
-    <t>0.9279,0.0023,0.0742,0.0009</t>
-  </si>
-  <si>
-    <t>0.0160,0.0064,0.9922,0.0002</t>
-  </si>
-  <si>
-    <t>0.4600,0.0031,0.7251,0.0005</t>
-  </si>
-  <si>
-    <t>0.9813,0.0004,0.0083,0.0012</t>
-  </si>
-  <si>
-    <t>0.9414,0.0017,0.0538,0.0028</t>
-  </si>
-  <si>
-    <t>0.9948,0.0002,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9416,0.0049,0.0593,0.0020</t>
-  </si>
-  <si>
-    <t>0.8415,0.0320,0.1275,0.0114</t>
-  </si>
-  <si>
-    <t>0.9716,0.0012,0.0199,0.0009</t>
-  </si>
-  <si>
-    <t>0.9911,0.0010,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.8539,0.0170,0.0935,0.0082</t>
-  </si>
-  <si>
-    <t>0.8398,0.0511,0.0473,0.0183</t>
-  </si>
-  <si>
-    <t>0.9575,0.0114,0.0010,0.0031</t>
-  </si>
-  <si>
-    <t>0.9814,0.0023,0.0005,0.0036</t>
-  </si>
-  <si>
-    <t>0.9830,0.0015,0.0002,0.0037</t>
-  </si>
-  <si>
-    <t>0.8591,0.0012,0.0003,0.1711</t>
-  </si>
-  <si>
-    <t>0.9912,0.0008,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.9834,0.0004,0.0045,0.0012</t>
-  </si>
-  <si>
-    <t>0.9904,0.0003,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.9645,0.0011,0.0358,0.0005</t>
-  </si>
-  <si>
-    <t>0.9779,0.0004,0.0077,0.0018</t>
-  </si>
-  <si>
-    <t>0.6099,0.0122,0.6255,0.0005</t>
-  </si>
-  <si>
-    <t>0.9703,0.0006,0.0333,0.0003</t>
-  </si>
-  <si>
-    <t>0.9047,0.0023,0.1503,0.0011</t>
-  </si>
-  <si>
-    <t>0.9758,0.0003,0.0467,0.0001</t>
-  </si>
-  <si>
-    <t>0.8486,0.0035,0.2481,0.0016</t>
-  </si>
-  <si>
-    <t>0.9517,0.0006,0.0001,0.0438</t>
-  </si>
-  <si>
-    <t>0.9862,0.0003,0.0007,0.0069</t>
-  </si>
-  <si>
-    <t>0.9534,0.0001,0.0001,0.0971</t>
-  </si>
-  <si>
-    <t>0.9355,0.0087,0.0045,0.0263</t>
-  </si>
-  <si>
-    <t>0.9469,0.0011,0.0009,0.0508</t>
-  </si>
-  <si>
-    <t>0.9730,0.0004,0.0002,0.0296</t>
-  </si>
-  <si>
-    <t>0.9163,0.0001,0.0001,0.2176</t>
-  </si>
-  <si>
-    <t>0.9528,0.0005,0.0004,0.0756</t>
-  </si>
-  <si>
-    <t>0.2981,0.1233,0.7168,0.0067</t>
-  </si>
-  <si>
-    <t>0.9645,0.0014,0.0152,0.0040</t>
-  </si>
-  <si>
-    <t>0.9176,0.0016,0.0084,0.0396</t>
-  </si>
-  <si>
-    <t>0.6817,0.0048,0.4717,0.0015</t>
-  </si>
-  <si>
-    <t>0.0039,0.0092,0.9908,0.0021</t>
-  </si>
-  <si>
-    <t>0.9223,0.0034,0.0852,0.0019</t>
-  </si>
-  <si>
-    <t>0.0223,0.0137,0.9912,0.0002</t>
-  </si>
-  <si>
-    <t>0.8940,0.0029,0.1165,0.0025</t>
-  </si>
-  <si>
-    <t>0.0756,0.0030,0.9657,0.0003</t>
-  </si>
-  <si>
-    <t>0.9134,0.0032,0.1116,0.0015</t>
-  </si>
-  <si>
-    <t>0.8975,0.0035,0.1491,0.0011</t>
-  </si>
-  <si>
-    <t>0.9483,0.0005,0.0579,0.0011</t>
-  </si>
-  <si>
-    <t>0.9701,0.0012,0.0226,0.0016</t>
-  </si>
-  <si>
-    <t>0.9940,0.0002,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9460,0.0014,0.0005,0.0443</t>
-  </si>
-  <si>
-    <t>0.8793,0.0075,0.0046,0.0957</t>
-  </si>
-  <si>
-    <t>0.9705,0.0004,0.0001,0.0425</t>
-  </si>
-  <si>
-    <t>0.8505,0.0028,0.0009,0.1411</t>
-  </si>
-  <si>
-    <t>0.9780,0.0003,0.0001,0.0237</t>
-  </si>
-  <si>
-    <t>0.9754,0.0027,0.0002,0.0037</t>
-  </si>
-  <si>
-    <t>0.9841,0.0007,0.0002,0.0079</t>
-  </si>
-  <si>
-    <t>0.9080,0.0012,0.0001,0.0783</t>
-  </si>
-  <si>
-    <t>0.9284,0.0071,0.0971,0.0004</t>
-  </si>
-  <si>
-    <t>0.5443,0.0544,0.4765,0.0005</t>
-  </si>
-  <si>
-    <t>0.5766,0.0029,0.7040,0.0002</t>
-  </si>
-  <si>
-    <t>0.9584,0.0019,0.0348,0.0009</t>
-  </si>
-  <si>
-    <t>0.3539,0.0036,0.8731,0.0002</t>
-  </si>
-  <si>
-    <t>0.9838,0.0004,0.0049,0.0015</t>
-  </si>
-  <si>
-    <t>0.8719,0.0009,0.2261,0.0006</t>
-  </si>
-  <si>
-    <t>0.9264,0.0013,0.0886,0.0015</t>
-  </si>
-  <si>
-    <t>0.7999,0.0014,0.0017,0.2601</t>
-  </si>
-  <si>
-    <t>0.9850,0.0001,0.0005,0.0058</t>
-  </si>
-  <si>
-    <t>0.8989,0.0004,0.0009,0.1104</t>
-  </si>
-  <si>
-    <t>0.9463,0.0000,0.0005,0.0463</t>
-  </si>
-  <si>
-    <t>0.6308,0.0000,0.0005,0.6134</t>
-  </si>
-  <si>
-    <t>0.9882,0.0004,0.0021,0.0014</t>
+    <t>0.9591,0.0043,0.0117,0.0155</t>
+  </si>
+  <si>
+    <t>0.1664,0.0004,0.0002,0.9596</t>
+  </si>
+  <si>
+    <t>0.9487,0.0038,0.0023,0.0533</t>
+  </si>
+  <si>
+    <t>0.3180,0.0003,0.0003,0.9056</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0025,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9729,0.0015,0.0450,0.0002</t>
+  </si>
+  <si>
+    <t>0.2436,0.0022,0.8838,0.0017</t>
+  </si>
+  <si>
+    <t>0.5289,0.0115,0.6282,0.0009</t>
+  </si>
+  <si>
+    <t>0.1785,0.0229,0.8597,0.0041</t>
+  </si>
+  <si>
+    <t>0.3633,0.0370,0.6040,0.0439</t>
+  </si>
+  <si>
+    <t>0.0007,0.9983,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9980,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.2498,0.8594,0.0051,0.0004</t>
+  </si>
+  <si>
+    <t>0.0019,0.9941,0.0048,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.9989,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.7772,0.0034,0.3368,0.0024</t>
+  </si>
+  <si>
+    <t>0.8430,0.0119,0.1740,0.0067</t>
+  </si>
+  <si>
+    <t>0.0041,0.0013,0.9949,0.0010</t>
+  </si>
+  <si>
+    <t>0.3902,0.0012,0.7829,0.0006</t>
+  </si>
+  <si>
+    <t>0.0165,0.0005,0.9934,0.0002</t>
+  </si>
+  <si>
+    <t>0.1199,0.0007,0.9497,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.0009,0.9968,0.0008</t>
+  </si>
+  <si>
+    <t>0.4155,0.6084,0.0526,0.0189</t>
+  </si>
+  <si>
+    <t>0.4138,0.2555,0.4864,0.0082</t>
+  </si>
+  <si>
+    <t>0.0182,0.0048,0.9849,0.0016</t>
+  </si>
+  <si>
+    <t>0.0289,0.9410,0.0061,0.0001</t>
+  </si>
+  <si>
+    <t>0.4969,0.5176,0.0469,0.0167</t>
+  </si>
+  <si>
+    <t>0.1811,0.0130,0.7978,0.0293</t>
+  </si>
+  <si>
+    <t>0.0904,0.9512,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0208,0.9719,0.0677,0.0024</t>
+  </si>
+  <si>
+    <t>0.0407,0.5086,0.3544,0.0228</t>
+  </si>
+  <si>
+    <t>0.0878,0.0024,0.9493,0.0007</t>
+  </si>
+  <si>
+    <t>0.4260,0.0033,0.7814,0.0007</t>
+  </si>
+  <si>
+    <t>0.0412,0.0010,0.9624,0.0045</t>
+  </si>
+  <si>
+    <t>0.0451,0.0225,0.9580,0.0004</t>
+  </si>
+  <si>
+    <t>0.0168,0.9426,0.0353,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.2493,0.0154,0.0022,0.8342</t>
+  </si>
+  <si>
+    <t>0.0047,0.9731,0.0485,0.0193</t>
+  </si>
+  <si>
+    <t>0.0074,0.9853,0.0099,0.0018</t>
+  </si>
+  <si>
+    <t>0.0009,0.9975,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.0067,0.0039,0.9818,0.0059</t>
+  </si>
+  <si>
+    <t>0.0034,0.0305,0.9966,0.0002</t>
+  </si>
+  <si>
+    <t>0.0694,0.0035,0.9330,0.0099</t>
+  </si>
+  <si>
+    <t>0.0381,0.0003,0.9783,0.0010</t>
+  </si>
+  <si>
+    <t>0.0487,0.0031,0.9620,0.0013</t>
+  </si>
+  <si>
+    <t>0.0113,0.0364,0.9787,0.0025</t>
+  </si>
+  <si>
+    <t>0.9888,0.0101,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9923,0.0015,0.0021,0.0017</t>
+  </si>
+  <si>
+    <t>0.9959,0.0014,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.0343,0.3913,0.8832,0.0402</t>
+  </si>
+  <si>
+    <t>0.9959,0.0016,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9946,0.0022,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0064,0.9298,0.8364,0.0025</t>
+  </si>
+  <si>
+    <t>0.1022,0.0279,0.9429,0.0013</t>
+  </si>
+  <si>
+    <t>0.0130,0.0019,0.9869,0.0010</t>
+  </si>
+  <si>
+    <t>0.0006,0.9426,0.9827,0.0004</t>
+  </si>
+  <si>
+    <t>0.0155,0.0011,0.9861,0.0007</t>
+  </si>
+  <si>
+    <t>0.0070,0.9870,0.0029,0.0006</t>
+  </si>
+  <si>
+    <t>0.0052,0.9948,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8870,0.0050,0.1911,0.0016</t>
+  </si>
+  <si>
+    <t>0.4271,0.0131,0.7893,0.0019</t>
+  </si>
+  <si>
+    <t>0.0056,0.0014,0.9924,0.0040</t>
+  </si>
+  <si>
+    <t>0.0014,0.9733,0.8778,0.0005</t>
+  </si>
+  <si>
+    <t>0.0126,0.9274,0.6338,0.0038</t>
+  </si>
+  <si>
+    <t>0.0268,0.9586,0.0547,0.0019</t>
+  </si>
+  <si>
+    <t>0.0018,0.9821,0.3117,0.0004</t>
+  </si>
+  <si>
+    <t>0.0064,0.0002,0.0080,0.9935</t>
+  </si>
+  <si>
+    <t>0.0041,0.0002,0.0002,0.9985</t>
+  </si>
+  <si>
+    <t>0.0023,0.0001,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.0091,0.0009,0.0008,0.9955</t>
+  </si>
+  <si>
+    <t>0.0092,0.0001,0.0002,0.9982</t>
+  </si>
+  <si>
+    <t>0.0142,0.0046,0.0023,0.9923</t>
+  </si>
+  <si>
+    <t>0.0002,0.9840,0.9882,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.5814,0.9917,0.0005</t>
+  </si>
+  <si>
+    <t>0.0068,0.7966,0.6758,0.0030</t>
+  </si>
+  <si>
+    <t>0.0047,0.2992,0.9169,0.0017</t>
+  </si>
+  <si>
+    <t>0.0053,0.9523,0.2135,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.8044,0.9737,0.0008</t>
+  </si>
+  <si>
+    <t>0.9973,0.0020,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0020,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0027,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9964,0.0013,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9980,0.0018,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0013,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9961,0.0033,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0007,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0335,0.0007,0.9867,0.0008</t>
+  </si>
+  <si>
+    <t>0.0640,0.0304,0.8922,0.0009</t>
+  </si>
+  <si>
+    <t>0.9724,0.0017,0.0160,0.0016</t>
+  </si>
+  <si>
+    <t>0.0107,0.0004,0.9922,0.0007</t>
+  </si>
+  <si>
+    <t>0.0331,0.9504,0.0009,0.0049</t>
+  </si>
+  <si>
+    <t>0.0041,0.9946,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0090,0.9835,0.0011,0.0025</t>
+  </si>
+  <si>
+    <t>0.0088,0.9878,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.0344,0.9744,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.0081,0.9836,0.0027,0.0039</t>
+  </si>
+  <si>
+    <t>0.6356,0.5067,0.0033,0.0017</t>
+  </si>
+  <si>
+    <t>0.5367,0.0313,0.4729,0.0410</t>
+  </si>
+  <si>
+    <t>0.2097,0.0145,0.8132,0.0116</t>
+  </si>
+  <si>
+    <t>0.5542,0.0986,0.3992,0.0419</t>
+  </si>
+  <si>
+    <t>0.8780,0.0229,0.1220,0.0058</t>
+  </si>
+  <si>
+    <t>0.0899,0.0301,0.0803,0.8722</t>
+  </si>
+  <si>
+    <t>0.0065,0.9891,0.0049,0.0010</t>
+  </si>
+  <si>
+    <t>0.0062,0.9878,0.0018,0.0036</t>
+  </si>
+  <si>
+    <t>0.0010,0.9885,0.0027,0.0214</t>
+  </si>
+  <si>
+    <t>0.0014,0.9746,0.7653,0.0012</t>
+  </si>
+  <si>
+    <t>0.0058,0.9881,0.0015,0.0022</t>
+  </si>
+  <si>
+    <t>0.9775,0.0254,0.0027,0.0013</t>
+  </si>
+  <si>
+    <t>0.7718,0.3170,0.0060,0.0041</t>
+  </si>
+  <si>
+    <t>0.9952,0.0007,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9962,0.0009,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9837,0.0066,0.0082,0.0019</t>
+  </si>
+  <si>
+    <t>0.9914,0.0021,0.0010,0.0026</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9844,0.0155,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9972,0.0002,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9962,0.0014,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.0028,0.6932,0.9894,0.0030</t>
+  </si>
+  <si>
+    <t>0.0357,0.2245,0.8034,0.0015</t>
+  </si>
+  <si>
+    <t>0.0378,0.0314,0.9537,0.0027</t>
+  </si>
+  <si>
+    <t>0.1426,0.1158,0.7868,0.0051</t>
+  </si>
+  <si>
+    <t>0.9868,0.0017,0.0037,0.0016</t>
+  </si>
+  <si>
+    <t>0.5941,0.0056,0.5428,0.0063</t>
+  </si>
+  <si>
+    <t>0.5120,0.0005,0.5968,0.0029</t>
+  </si>
+  <si>
+    <t>0.8081,0.0171,0.1211,0.0292</t>
+  </si>
+  <si>
+    <t>0.1312,0.0006,0.0007,0.9696</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0212,0.0002,0.0000,0.9963</t>
+  </si>
+  <si>
+    <t>0.0106,0.0001,0.0005,0.9974</t>
+  </si>
+  <si>
+    <t>0.0022,0.9819,0.0737,0.0006</t>
+  </si>
+  <si>
+    <t>0.9963,0.0018,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0139,0.9746,0.0098,0.0076</t>
+  </si>
+  <si>
+    <t>0.9936,0.0003,0.0005,0.0029</t>
+  </si>
+  <si>
+    <t>0.8313,0.1786,0.0266,0.0052</t>
+  </si>
+  <si>
+    <t>0.9943,0.0004,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.0671,0.0028,0.0011,0.9765</t>
+  </si>
+  <si>
+    <t>0.9956,0.0004,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.0247,0.2120,0.9443,0.0525</t>
+  </si>
+  <si>
+    <t>0.6401,0.0003,0.0002,0.7079</t>
+  </si>
+  <si>
+    <t>0.9792,0.0037,0.0004,0.0113</t>
+  </si>
+  <si>
+    <t>0.6399,0.4884,0.0032,0.0010</t>
+  </si>
+  <si>
+    <t>0.9566,0.0152,0.0114,0.0079</t>
+  </si>
+  <si>
+    <t>0.9446,0.0185,0.0136,0.0146</t>
+  </si>
+  <si>
+    <t>0.0251,0.9537,0.0085,0.0120</t>
+  </si>
+  <si>
+    <t>0.9697,0.0108,0.0102,0.0033</t>
+  </si>
+  <si>
+    <t>0.9602,0.0133,0.0253,0.0031</t>
+  </si>
+  <si>
+    <t>0.9964,0.0015,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9978,0.0002,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9948,0.0016,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.9967,0.0003,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9963,0.0003,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9923,0.0079,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.6422,0.5844,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.8734,0.1702,0.0021,0.0037</t>
+  </si>
+  <si>
+    <t>0.0130,0.3074,0.9531,0.0055</t>
+  </si>
+  <si>
+    <t>0.9878,0.0184,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9758,0.0216,0.0034,0.0033</t>
+  </si>
+  <si>
+    <t>0.9967,0.0010,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.8651,0.2118,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.0016,0.0039,0.9978,0.0006</t>
+  </si>
+  <si>
+    <t>0.9866,0.0062,0.0042,0.0019</t>
+  </si>
+  <si>
+    <t>0.0006,0.0011,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0088,0.0584,0.9888,0.0023</t>
+  </si>
+  <si>
+    <t>0.0227,0.0085,0.9740,0.0045</t>
+  </si>
+  <si>
+    <t>0.0147,0.0124,0.9875,0.0008</t>
+  </si>
+  <si>
+    <t>0.0018,0.0007,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0003,0.9979,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.0007,0.9966,0.0004</t>
+  </si>
+  <si>
+    <t>0.0071,0.0025,0.9873,0.0025</t>
+  </si>
+  <si>
+    <t>0.2759,0.0203,0.7783,0.0131</t>
+  </si>
+  <si>
+    <t>0.0224,0.0043,0.9672,0.0034</t>
+  </si>
+  <si>
+    <t>0.4923,0.0338,0.4763,0.0020</t>
+  </si>
+  <si>
+    <t>0.2597,0.2384,0.5712,0.0172</t>
+  </si>
+  <si>
+    <t>0.1175,0.8161,0.0553,0.0094</t>
+  </si>
+  <si>
+    <t>0.7243,0.0111,0.3122,0.0200</t>
+  </si>
+  <si>
+    <t>0.5641,0.0824,0.4478,0.0042</t>
+  </si>
+  <si>
+    <t>0.7720,0.2933,0.0190,0.0009</t>
+  </si>
+  <si>
+    <t>0.4594,0.6812,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9887,0.0209,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9838,0.0252,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.2823,0.8266,0.0028,0.0036</t>
+  </si>
+  <si>
+    <t>0.8636,0.0338,0.1014,0.0125</t>
+  </si>
+  <si>
+    <t>0.9520,0.0006,0.0420,0.0023</t>
+  </si>
+  <si>
+    <t>0.9280,0.0073,0.0271,0.0180</t>
+  </si>
+  <si>
+    <t>0.9668,0.0009,0.0490,0.0007</t>
+  </si>
+  <si>
+    <t>0.0922,0.0040,0.9141,0.0179</t>
+  </si>
+  <si>
+    <t>0.0088,0.0009,0.9924,0.0018</t>
+  </si>
+  <si>
+    <t>0.0644,0.2988,0.9217,0.0178</t>
+  </si>
+  <si>
+    <t>0.0146,0.0042,0.9863,0.0009</t>
+  </si>
+  <si>
+    <t>0.2082,0.2121,0.5828,0.0180</t>
+  </si>
+  <si>
+    <t>0.0029,0.0017,0.9927,0.0005</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9948,0.0028,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9965,0.0028,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0015,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0016,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0020,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.1071,0.9945,0.0019</t>
+  </si>
+  <si>
+    <t>0.0949,0.0921,0.7823,0.0184</t>
+  </si>
+  <si>
+    <t>0.8520,0.0061,0.0907,0.0245</t>
+  </si>
+  <si>
+    <t>0.0084,0.0015,0.9905,0.0005</t>
+  </si>
+  <si>
+    <t>0.0117,0.0026,0.9790,0.0043</t>
+  </si>
+  <si>
+    <t>0.0141,0.0753,0.9665,0.0039</t>
+  </si>
+  <si>
+    <t>0.0194,0.0011,0.9896,0.0005</t>
+  </si>
+  <si>
+    <t>0.0052,0.0041,0.9855,0.0016</t>
+  </si>
+  <si>
+    <t>0.0157,0.0098,0.9896,0.0013</t>
+  </si>
+  <si>
+    <t>0.0096,0.0010,0.9883,0.0011</t>
+  </si>
+  <si>
+    <t>0.0213,0.0527,0.9290,0.0088</t>
+  </si>
+  <si>
+    <t>0.9176,0.0006,0.1128,0.0015</t>
+  </si>
+  <si>
+    <t>0.8321,0.0004,0.2572,0.0011</t>
+  </si>
+  <si>
+    <t>0.5797,0.0023,0.4363,0.0127</t>
+  </si>
+  <si>
+    <t>0.9927,0.0063,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9912,0.0112,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9988,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0041,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9982,0.0009,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0005,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0586,0.0228,0.9178,0.0021</t>
+  </si>
+  <si>
+    <t>0.0017,0.0056,0.9951,0.0006</t>
+  </si>
+  <si>
+    <t>0.0018,0.0052,0.9964,0.0008</t>
+  </si>
+  <si>
+    <t>0.0146,0.0239,0.9385,0.0032</t>
+  </si>
+  <si>
+    <t>0.0078,0.0022,0.9928,0.0002</t>
+  </si>
+  <si>
+    <t>0.0056,0.0029,0.8995,0.4932</t>
+  </si>
+  <si>
+    <t>0.1329,0.0028,0.9195,0.0039</t>
+  </si>
+  <si>
+    <t>0.0654,0.0011,0.7020,0.0483</t>
+  </si>
+  <si>
+    <t>0.4430,0.0042,0.0061,0.6661</t>
+  </si>
+  <si>
+    <t>0.0464,0.0274,0.0013,0.9716</t>
+  </si>
+  <si>
+    <t>0.0291,0.0003,0.0036,0.9791</t>
+  </si>
+  <si>
+    <t>0.0020,0.0001,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.7909,0.0033,0.0029,0.2105</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2177,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
         <v>280</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2415,7 +2415,7 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
         <v>297</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3899,7 +3899,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
         <v>403</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4123,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
         <v>419</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
